--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12751,22 +12751,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13039,22 +13039,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12623,22 +12623,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12569,12 +12569,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -12655,22 +12655,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12847,22 +12847,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳光明区光明万达广场</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳光明区光明万达广场</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>光明大道6号深圳光明万达广场F1层1号门中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -12761,12 +12761,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海延安西路特斯拉中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市闵行区延安西路3180号</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海延安西路特斯拉中心</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区延安西路3180号</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京西北旺万象汇</t>
+          <t>蔚来空间 | 北京丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
+          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京丽泽龙湖天街</t>
+          <t>蔚来空间 | 北京西北旺万象汇</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>北京市丰台区龙湖丽泽天街1F-07商铺</t>
+          <t>北京市海淀区后厂村路99号西北旺万象汇L102号商铺</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -12559,22 +12559,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,14 +12840,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,29 +13320,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>华为授权体验店（K11）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>华为授权体验店（K11 ECOAST）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（K11 ECOAST）</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13455,22 +13455,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海闵行区仲盛世界商城</t>
+          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
+          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 75%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13529,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区吴宝路销售服务中心</t>
+          <t>小米汽车上海闵行区仲盛世界商城</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区虹桥机场销售服务中心</t>
+          <t>小米汽车上海市闵行区仲盛世界商城城市展</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260525_vs_20260601.xlsx
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>上海复地活力城</t>
+          <t>上海静安大融城</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
+          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>上海静安大融城</t>
+          <t>上海复地活力城</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>上海市静安区彭浦镇沪太路1111号1#A-02 B门中庭</t>
+          <t>上海市浦东新区沪南路2229号一层L1-QT-022</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为智能生活馆•石家庄欢乐汇</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
+          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•石家庄欢乐汇</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>河北省石家庄市裕华区裕泰路77号欢乐汇100FUN CITY1F</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
+          <t>小米汽车四川成都金牛区金牛万达</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
+          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小米汽车四川成都金牛区金牛万达</t>
+          <t>小米汽车四川成都郫都区龙湖蜀新天街</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>一环路北三段 1 栋 1 号成都金牛万达广场 1F 层</t>
+          <t>龙湖成都蜀新天街星悦荟A馆-1F-26/27</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
+          <t>小米汽车山东青岛胶州龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车山东青岛胶州龙湖天街</t>
+          <t>小米汽车山东青岛黄岛区黄岛融创茂</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>山东省青岛市黄岛区滨海大道2777号融创茂1楼中庭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
+          <t>小米汽车广东深圳宝安区大悦城</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>龙岗万达广场商场一楼中庭</t>
+          <t>创业二路59-4大悦城购物中心L1层中庭</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区大悦城</t>
+          <t>小米汽车广东深圳龙岗区深圳龙岗万达</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>创业二路59-4大悦城购物中心L1层中庭</t>
+          <t>龙岗万达广场商场一楼中庭</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
+          <t>小米汽车浙江杭州余杭区余杭万达</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>延安路609号国大城市广场1楼</t>
+          <t>文一西路1888号</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
+          <t>小米汽车浙江杭州拱墅区国大城市广场</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>九沙大道388号国芳天街B馆1楼</t>
+          <t>延安路609号国大城市广场1楼</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区余杭万达</t>
+          <t>小米汽车浙江杭州上城区龙湖国芳天街</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>文一西路1888号</t>
+          <t>九沙大道388号国芳天街B馆1楼</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>青岛青特万达广场新能源空间</t>
+          <t>青岛李沧万达广场新能源空间</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市城阳区正阳中路114号</t>
+          <t>山东省青岛市李沧区巨峰路173号巷</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>青岛李沧万达广场新能源空间</t>
+          <t>青岛青特万达广场新能源空间</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区巨峰路173号巷</t>
+          <t>山东省青岛市城阳区正阳中路114号</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安阳文昌大道销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
+          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
+          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
+          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>新疆中盛国奥汽车销售服务有限公司</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
+          <t>中国江苏省扬州市邗江区名车路8号 → 扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安曲江</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车佛山南庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市桃城区昌明大街与胜利西路交口南行20米路西 → 河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车上海张江销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区水清沟大沙支路2号 → 青岛市市北区四流南路22号-8幢展厅</t>
+          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海张江销售展厅</t>
+          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区育仁路188弄4号 → 上海市浦东新区育仁路188弄4号一层</t>
+          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>保定市莲池区东二环422号贺阳中学北行500米路西 → 河北省保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>湖南省常德市武陵区东江街道新安社区启明中路(武陵工业新区101-01号) → 小鹏汽车常德大道销售中心</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼洁路10号 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州新能源汽车城销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市沧县捷地乡捷地村南绕城路南 → 河北省沧州市新华区捷地乡捷地村南绕城路南</t>
+          <t>上海市青浦区香花桥街道北青公路9595号 → 上海市青浦区香花桥街道北青公路9559号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>宾利北京亦庄</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>宾利南昌</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
+          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山南庄销售服务中心</t>
+          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区南庄镇樵乐路(吉利大道西)杜村工业区5号 → 佛山市禅城区南庄镇醒群社村工业区5号</t>
+          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车安阳文昌大道销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
+          <t>安阳市文昌大道与东风路西北角 → 安阳市文峰区文昌大道与东风路交叉口西南角</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区卫津南路与绥江桥东南100米 → 天津市西青区李七庄街卫津南路绥江桥东南100米</t>
+          <t>第四大道S107-S109 前兴路润城 650228 → 日新东路259号 西山区 650103</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车石家庄长安汽车园销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>石家庄长安区太行北大街55号汽车园B区4号 → 河北省石家庄市长安区太行北大街55号汽车园B区4号</t>
+          <t>小米之家(蚌埠蚌山区银泰专卖店) → 东海大道银泰百货1F小米之家</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利南昌</t>
+          <t>新疆中盛国奥汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新兴西大道149号（店面）101室 望城新区 330103 → 新兴西大道198号 望城新区 330103</t>
+          <t>新疆维吾尔自治区乌鲁木齐市头屯河区乌鲁木齐市高新区乌昌路2094号汇京汽车城第05栋 → 新疆维吾尔自治区乌鲁木齐市新市区北辰七街3888号北城国际新能源汽车城7号展厅</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车成都空港销售服务中心</t>
+          <t>蔚来体验中心 | 西安曲江</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
+          <t>陕西省西安市灞桥区东三环与南三环交汇处东高端汽车产业园 → 陕西省西安市灞桥区东三环与南三环交汇处灞桥东城高端汽车主题公园</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京亦庄</t>
+          <t>小鹏汽车成都空港销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>中和街16号3幢1001-1002单元 经济技术开发区 100038 → 中和街16号3幢1001-1002单元 经济技术开发区 100176</t>
+          <t>成都市双流区成双大道南段566号 → 四川省成都市双流区成双大道南段566号</t>
         </is>
       </c>
     </row>
@@ -13268,17 +13268,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>小鹏汽车徐州两山口销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州两山口销售展厅 → 小鹏汽车徐州两山口销售中心</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
@@ -13359,22 +13359,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东威海环翠区威高广场</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府和悦广场</t>
+          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>小米汽车山东威海环翠区威高广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴桐乡万象汇</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区吾悦广场汽车体验专卖店</t>
+          <t>小米汽车四川成都双流区天府和悦广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省宿州市埇桥区宿州吾悦广场汽车体验店</t>
+          <t>小米汽车四川省成都市双流区天府和悦广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
